--- a/backend/data/financials_by_company/1832.SR.xlsx
+++ b/backend/data/financials_by_company/1832.SR.xlsx
@@ -4169,10 +4169,8 @@
           <t>Riyadh</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>14342</t>
-        </is>
+      <c r="D2" t="n">
+        <v>14342</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4386,7 +4384,7 @@
         <v>-563306</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -4523,7 +4521,7 @@
         </is>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>0.05820012</v>
